--- a/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-10.xlsx
+++ b/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-10.xlsx
@@ -474,592 +474,592 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>5583988866605</v>
+        <v>5583988037929</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Joanita</t>
+          <t>Alisson</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Joanita Barbosa Miranda de Souza</t>
+          <t>Alisson Francisco Carvalho da Silva</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>5581992872987</v>
+        <v>5583997247219</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Ednaldo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jose Antonio da Silva-Zito Som</t>
+          <t>Ednaldo Quirino Meireles</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>5581991712740</v>
+        <v>5583998291227</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Claudio</t>
+          <t>Cristiano</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Claudio Nascimento de Araujo</t>
+          <t>Cristiano Santos da Silva</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>5583986004026</v>
+        <v>5583981982467</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Martorelli</t>
+          <t>Fundacao</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Martorelli Jose da Silva</t>
+          <t>Fundacao Casulo</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>5583986762176</v>
+        <v>5583988947368</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Luiz</t>
+          <t>Joyce</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Luiz Joaquim de Souza</t>
+          <t>Joyce Conde Pereira</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>5583998640543</v>
+        <v>5583988866605</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Deoberto</t>
+          <t>Joanita</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Deoberto Lobo dos Santos</t>
+          <t>Joanita Barbosa Miranda de Souza</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>5583988972610</v>
+        <v>5581992872987</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ivanildo</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ivanildo Bandeira</t>
+          <t>Jose Antonio da Silva-Zito Som</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>5583988158490</v>
+        <v>5581991712740</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Keyla</t>
+          <t>Claudio</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Keyla Oliveira de Souza</t>
+          <t>Claudio Nascimento de Araujo</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>5583987453905</v>
+        <v>5583986004026</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Severino</t>
+          <t>Martorelli</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Severino Paulo dos Santos</t>
+          <t>Martorelli Jose da Silva</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>5583987143255</v>
+        <v>5583986762176</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Luiz</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Maria das Gracas Ramalho</t>
+          <t>Luiz Joaquim de Souza</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>5583998130074</v>
+        <v>5583998640543</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Wilma</t>
+          <t>Deoberto</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wilma Lopes</t>
+          <t>Deoberto Lobo dos Santos</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>5583981647220</v>
+        <v>5583988972610</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Juciane</t>
+          <t>Ivanildo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Juciane Nobrega Lima</t>
+          <t>Ivanildo Bandeira</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>5583987263538</v>
+        <v>5583988158490</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Wagner</t>
+          <t>Keyla</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Wagner do Nascimento</t>
+          <t>Keyla Oliveira de Souza</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>5583988808310</v>
+        <v>5583987453905</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Eudes</t>
+          <t>Severino</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Eudes Lopes Cavalcanti</t>
+          <t>Severino Paulo dos Santos</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>5583986170985</v>
+        <v>5583987143255</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Arielly</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Arielly Rebeka do Nascimento Souza</t>
+          <t>Maria das Gracas Ramalho</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>5583998600229</v>
+        <v>5583998130074</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Aurelio</t>
+          <t>Wilma</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Aurelio Albuquerque</t>
+          <t>Wilma Lopes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>5583988909083</v>
+        <v>5583981647220</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Helio</t>
+          <t>Juciane</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Helio Tomaz Goncalves</t>
+          <t>Juciane Nobrega Lima</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>5583988124482</v>
+        <v>5583987263538</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Joao</t>
+          <t>Wagner</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Joao Batista do Nascimento</t>
+          <t>Wagner do Nascimento</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>5583987804772</v>
+        <v>5583988808310</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rodrigo</t>
+          <t>Eudes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Rodrigo Fernandes</t>
+          <t>Eudes Lopes Cavalcanti</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="3">
       <c r="A21" s="4" t="n">
-        <v>5583987167238</v>
+        <v>5583986170985</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Arielly</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ana Maria Morais Fernandes</t>
+          <t>Arielly Rebeka do Nascimento Souza</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="3">
       <c r="A22" s="4" t="n">
-        <v>5583987938292</v>
+        <v>5583998600229</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ricardo</t>
+          <t>Aurelio</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ricardo Pinto Leitao</t>
+          <t>Aurelio Albuquerque</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="3">
       <c r="A23" s="4" t="n">
-        <v>5583991282982</v>
+        <v>5583988909083</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Erick</t>
+          <t>Helio</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Erick Cardoso da Silva</t>
+          <t>Helio Tomaz Goncalves</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="3">
       <c r="A24" s="4" t="n">
-        <v>5583987761053</v>
+        <v>5583988124482</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Elisangela</t>
+          <t>Joao</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Elisangela Ferreira de Queiroz</t>
+          <t>Joao Batista do Nascimento</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="3">
       <c r="A25" s="4" t="n">
-        <v>5583999410834</v>
+        <v>5583987804772</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Everclean</t>
+          <t>Rodrigo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Everclean</t>
+          <t>Rodrigo Fernandes</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="3">
       <c r="A26" s="4" t="n">
-        <v>5585992688423</v>
+        <v>5583993914418</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Victor</t>
+          <t>Yasmin</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Victor Silva Rodrigues</t>
+          <t>Yasmin Vitoria Lino Andrade da Silva</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="3">
       <c r="A27" s="4" t="n">
-        <v>5583987908690</v>
+        <v>5583987167238</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Glacai</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Glacai</t>
+          <t>Ana Maria Morais Fernandes</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="3">
       <c r="A28" s="4" t="n">
-        <v>5583981372592</v>
+        <v>5583987938292</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Claudete</t>
+          <t>Ricardo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Claudete da Silva Goncalves</t>
+          <t>Ricardo Pinto Leitao</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="3">
       <c r="A29" s="4" t="n">
-        <v>5583987649917</v>
+        <v>5583991282982</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Rosangela</t>
+          <t>Erick</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Rosangela da Silva Santos</t>
+          <t>Erick Cardoso da Silva</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="3">
       <c r="A30" s="4" t="n">
-        <v>5583988578278</v>
+        <v>5583987761053</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Rodrigo</t>
+          <t>Elisangela</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Rodrigo Diniz Junior</t>
+          <t>Elisangela Ferreira de Queiroz</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="3">
       <c r="A31" s="4" t="n">
-        <v>5583987082035</v>
+        <v>5583999410834</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dailson</t>
+          <t>Everclean</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dailson Pessoa da Silva</t>
+          <t>Everclean</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="3">
       <c r="A32" s="4" t="n">
-        <v>5583996190736</v>
+        <v>5585992688423</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Marcos</t>
+          <t>Victor</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Marcos Vanderley Batista</t>
+          <t>Victor Silva Rodrigues</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="3">
       <c r="A33" s="4" t="n">
-        <v>5583986123363</v>
+        <v>5583987908690</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Glacai</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Anna Elizabeth Goncalves de Medeiros</t>
+          <t>Glacai</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="3">
       <c r="A34" s="4" t="n">
-        <v>5583993132611</v>
+        <v>5583981372592</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Joaquim</t>
+          <t>Claudete</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Joaquim Francilino Silva Filho</t>
+          <t>Claudete da Silva Goncalves</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="3">
       <c r="A35" s="4" t="n">
-        <v>5583986723096</v>
+        <v>5583987649917</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Rosangela</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jose Matheus Meira Borges</t>
+          <t>Rosangela da Silva Santos</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="3">
       <c r="A36" s="4" t="n">
-        <v>5583986602589</v>
+        <v>5583988578278</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Alexandra</t>
+          <t>Rodrigo</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Alexandra Bernardino da Silva</t>
+          <t>Rodrigo Diniz Junior</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="3">
       <c r="A37" s="4" t="n">
-        <v>5583988060247</v>
+        <v>5583987082035</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Leandro</t>
+          <t>Dailson</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Leandro Emanuel Gomes Monteiro</t>
+          <t>Dailson Pessoa da Silva</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="3">
       <c r="A38" s="4" t="n">
-        <v>5583988344551</v>
+        <v>5583996190736</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Geisiele</t>
+          <t>Marcos</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Geisiele Bernardo da Silva</t>
+          <t>Marcos Vanderley Batista</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="3">
       <c r="A39" s="4" t="n">
-        <v>5583993794908</v>
+        <v>5583986123363</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jose Edmilson Barbosa de Lima</t>
+          <t>Anna Elizabeth Goncalves de Medeiros</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="3">
       <c r="A40" s="4" t="n">
-        <v>5588997057085</v>
+        <v>5583993132611</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kaio</t>
+          <t>Joaquim</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kaio Gomes Pontes</t>
+          <t>Joaquim Francilino Silva Filho</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="3">
       <c r="A41" s="4" t="n">
-        <v>5583987977486</v>
+        <v>5583986723096</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1068,58 +1068,58 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jose Elias de Oliveira</t>
+          <t>Jose Matheus Meira Borges</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="3">
       <c r="A42" s="4" t="n">
-        <v>5583996840027</v>
+        <v>5583986602589</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Endovideo</t>
+          <t>Alexandra</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Endovideo</t>
+          <t>Alexandra Bernardino da Silva</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="3">
       <c r="A43" s="4" t="n">
-        <v>5531975995605</v>
+        <v>5583988060247</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Colegio</t>
+          <t>Leandro</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Colegio Batista Brasil - Praia - Joao Pessoa</t>
+          <t>Leandro Emanuel Gomes Monteiro</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="3">
       <c r="A44" s="4" t="n">
-        <v>5583996676777</v>
+        <v>5583988344551</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Gustavo</t>
+          <t>Geisiele</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Gustavo Brunner Oliveira Vieira</t>
+          <t>Geisiele Bernardo da Silva</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="3">
       <c r="A45" s="4" t="n">
-        <v>5583988091508</v>
+        <v>5583993794908</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -1128,97 +1128,97 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jose Gilvandro da Silva Santos</t>
+          <t>Jose Edmilson Barbosa de Lima</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="3">
       <c r="A46" s="4" t="n">
-        <v>5583999673160</v>
+        <v>5588997057085</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Zarqueu</t>
+          <t>Kaio</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Zarqueu Manoel da Silva</t>
+          <t>Kaio Gomes Pontes</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="3">
       <c r="A47" s="4" t="n">
-        <v>5583991210505</v>
+        <v>5583987977486</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Maria Beatriz Lima do Nascimento</t>
+          <t>Jose Elias de Oliveira</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="3">
       <c r="A48" s="4" t="n">
-        <v>5583993912051</v>
+        <v>5583996840027</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ricardo</t>
+          <t>Endovideo</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ricardo Lira</t>
+          <t>Endovideo</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="3">
       <c r="A49" s="4" t="n">
-        <v>5583996736779</v>
+        <v>5531975995605</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Colegio</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Maria das Dores Silva</t>
+          <t>Colegio Batista Brasil - Praia - Joao Pessoa</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="3">
       <c r="A50" s="4" t="n">
-        <v>5583999154417</v>
+        <v>5583996676777</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Leandro</t>
+          <t>Gustavo</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Leandro do Nascimento Silva</t>
+          <t>Gustavo Brunner Oliveira Vieira</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="3">
       <c r="A51" s="4" t="n">
-        <v>5583991392674</v>
+        <v>5583988091508</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Felipe</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Felipe Pereira</t>
+          <t>Jose Gilvandro da Silva Santos</t>
         </is>
       </c>
     </row>
